--- a/pages/WR_progressions/Medals_Men_IP.xlsx
+++ b/pages/WR_progressions/Medals_Men_IP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FE3893-2160-461F-87F5-8656301D4E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A2C5EB-D1A4-4156-9198-2BDA9A907A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="13">
   <si>
     <t>8th</t>
   </si>
@@ -82,7 +82,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="164" formatCode="mm:ss.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -115,8 +115,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1400477D-CA59-426F-9BF4-08585135C868}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -464,7 +466,7 @@
     <col min="12" max="12" width="11.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -502,1032 +504,1083 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <f>H2/86400</f>
+        <v>2.769722222222222E-3</v>
+      </c>
+      <c r="D2" s="1">
+        <f t="shared" ref="D2:G2" si="0">I2/86400</f>
+        <v>2.7812037037037037E-3</v>
+      </c>
+      <c r="E2" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7971180555555553E-3</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" si="0"/>
+        <v>2.8775810185185185E-3</v>
+      </c>
+      <c r="G2" s="1">
+        <f t="shared" si="0"/>
+        <v>2.9595023148148145E-3</v>
+      </c>
+      <c r="H2">
+        <v>239.304</v>
+      </c>
+      <c r="I2">
+        <v>240.29599999999999</v>
+      </c>
+      <c r="J2">
+        <v>241.67099999999999</v>
+      </c>
+      <c r="K2" s="2">
+        <v>248.62299999999999</v>
+      </c>
+      <c r="L2" s="2">
+        <v>255.70099999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3">
         <v>2023</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1">
         <v>2.7933333333333334E-3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D3" s="1">
         <v>2.8120486111111111E-3</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E3" s="1">
         <v>2.8517708333333333E-3</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F3" s="1">
         <v>2.891203703703704E-3</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G3" s="1">
         <v>2.9494212962962963E-3</v>
       </c>
-      <c r="H2" s="2">
-        <f>86400*C2</f>
+      <c r="H3">
+        <f>86400*C3</f>
         <v>241.34400000000002</v>
       </c>
-      <c r="I2" s="2">
-        <f t="shared" ref="I2:L2" si="0">86400*D2</f>
+      <c r="I3">
+        <f t="shared" ref="I3:L3" si="1">86400*D3</f>
         <v>242.96099999999998</v>
       </c>
-      <c r="J2" s="2">
-        <f t="shared" si="0"/>
+      <c r="J3">
+        <f t="shared" si="1"/>
         <v>246.393</v>
       </c>
-      <c r="K2" s="2">
-        <f t="shared" si="0"/>
+      <c r="K3">
+        <f t="shared" si="1"/>
         <v>249.8</v>
       </c>
-      <c r="L2" s="2">
-        <f t="shared" si="0"/>
+      <c r="L3">
+        <f t="shared" si="1"/>
         <v>254.83</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4">
         <v>2022</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
         <v>2.7857986111111113E-3</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D4" s="1">
         <v>2.8126388888888888E-3</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E4" s="1">
         <v>2.8377430555555556E-3</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F4" s="1">
         <v>2.8889699074074074E-3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G4" s="1">
         <v>2.9803125000000003E-3</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H25" si="1">86400*C3</f>
+      <c r="H4">
+        <f t="shared" ref="H4:H26" si="2">86400*C4</f>
         <v>240.69300000000001</v>
       </c>
-      <c r="I3" s="2">
-        <f t="shared" ref="I3:I25" si="2">86400*D3</f>
+      <c r="I4">
+        <f t="shared" ref="I4:I26" si="3">86400*D4</f>
         <v>243.012</v>
       </c>
-      <c r="J3" s="2">
-        <f t="shared" ref="J3:J25" si="3">86400*E3</f>
+      <c r="J4">
+        <f t="shared" ref="J4:J26" si="4">86400*E4</f>
         <v>245.18100000000001</v>
       </c>
-      <c r="K3" s="2">
-        <f t="shared" ref="K3:K25" si="4">86400*F3</f>
+      <c r="K4">
+        <f t="shared" ref="K4:K26" si="5">86400*F4</f>
         <v>249.607</v>
       </c>
-      <c r="L3" s="2">
-        <f t="shared" ref="L3:L25" si="5">86400*G3</f>
+      <c r="L4">
+        <f t="shared" ref="L4:L25" si="6">86400*G4</f>
         <v>257.49900000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5">
         <v>2021</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1">
         <v>2.8152430555555556E-3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D5" s="1">
         <v>2.8447337962962962E-3</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E5" s="1">
         <v>2.8518749999999998E-3</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F5" s="1">
         <v>2.937962962962963E-3</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G5" s="1">
         <v>3.0406944444444444E-3</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" si="1"/>
+      <c r="H5">
+        <f t="shared" si="2"/>
         <v>243.23699999999999</v>
       </c>
-      <c r="I4" s="2">
-        <f t="shared" si="2"/>
+      <c r="I5">
+        <f t="shared" si="3"/>
         <v>245.785</v>
       </c>
-      <c r="J4" s="2">
-        <f t="shared" si="3"/>
+      <c r="J5">
+        <f t="shared" si="4"/>
         <v>246.40199999999999</v>
       </c>
-      <c r="K4" s="2">
-        <f t="shared" si="4"/>
+      <c r="K5">
+        <f t="shared" si="5"/>
         <v>253.84</v>
       </c>
-      <c r="L4" s="2">
-        <f t="shared" si="5"/>
+      <c r="L5">
+        <f t="shared" si="6"/>
         <v>262.71600000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6">
         <v>2020</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
         <v>2.8001620370370372E-3</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D6" s="1">
         <v>2.8199074074074073E-3</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E6" s="1">
         <v>2.8656597222222221E-3</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F6" s="1">
         <v>2.9031134259259262E-3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G6" s="1">
         <v>3.0261805555555554E-3</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="1"/>
+      <c r="H6">
+        <f t="shared" si="2"/>
         <v>241.93400000000003</v>
       </c>
-      <c r="I5" s="2">
-        <f t="shared" si="2"/>
+      <c r="I6">
+        <f t="shared" si="3"/>
         <v>243.64</v>
       </c>
-      <c r="J5" s="2">
-        <f t="shared" si="3"/>
+      <c r="J6">
+        <f t="shared" si="4"/>
         <v>247.59299999999999</v>
       </c>
-      <c r="K5" s="2">
-        <f t="shared" si="4"/>
+      <c r="K6">
+        <f t="shared" si="5"/>
         <v>250.82900000000001</v>
       </c>
-      <c r="L5" s="2">
-        <f t="shared" si="5"/>
+      <c r="L6">
+        <f t="shared" si="6"/>
         <v>261.46199999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="N6">
+        <v>239.304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7">
         <v>2019</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
         <v>2.864074074074074E-3</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D7" s="1">
         <v>2.8829976851851855E-3</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E7" s="1">
         <v>2.9139351851851852E-3</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F7" s="1">
         <v>2.969710648148148E-3</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" s="1">
         <v>3.0736342592592595E-3</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="1"/>
+      <c r="H7">
+        <f t="shared" si="2"/>
         <v>247.45599999999999</v>
       </c>
-      <c r="I6" s="2">
-        <f t="shared" si="2"/>
+      <c r="I7">
+        <f t="shared" si="3"/>
         <v>249.09100000000004</v>
       </c>
-      <c r="J6" s="2">
-        <f t="shared" si="3"/>
+      <c r="J7">
+        <f t="shared" si="4"/>
         <v>251.76400000000001</v>
       </c>
-      <c r="K6" s="2">
-        <f t="shared" si="4"/>
+      <c r="K7">
+        <f t="shared" si="5"/>
         <v>256.58299999999997</v>
       </c>
-      <c r="L6" s="2">
-        <f t="shared" si="5"/>
+      <c r="L7">
+        <f t="shared" si="6"/>
         <v>265.56200000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7">
+      <c r="N7">
+        <v>240.29599999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8">
         <v>2018</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
         <v>2.9208912037037038E-3</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D8" s="1">
         <v>2.9354398148148148E-3</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1">
         <v>2.9401041666666668E-3</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <v>3.013935185185185E-3</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" s="1">
         <v>3.0857175925925926E-3</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" si="1"/>
+      <c r="H8">
+        <f t="shared" si="2"/>
         <v>252.36500000000001</v>
       </c>
-      <c r="I7" s="2">
-        <f t="shared" si="2"/>
+      <c r="I8">
+        <f t="shared" si="3"/>
         <v>253.62199999999999</v>
       </c>
-      <c r="J7" s="2">
-        <f t="shared" si="3"/>
+      <c r="J8">
+        <f t="shared" si="4"/>
         <v>254.02500000000001</v>
       </c>
-      <c r="K7" s="2">
-        <f t="shared" si="4"/>
+      <c r="K8">
+        <f t="shared" si="5"/>
         <v>260.404</v>
       </c>
-      <c r="L7" s="2">
-        <f t="shared" si="5"/>
+      <c r="L8">
+        <f t="shared" si="6"/>
         <v>266.60599999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8">
+      <c r="N8">
+        <v>241.67099999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9">
         <v>2017</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
         <v>2.9186574074074076E-3</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>2.9473032407407408E-3</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E9" s="1">
         <v>2.960578703703704E-3</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F9" s="1">
         <v>3.0048726851851851E-3</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9" s="1">
         <v>3.0537384259259263E-3</v>
       </c>
-      <c r="H8" s="2">
-        <f t="shared" si="1"/>
+      <c r="H9">
+        <f t="shared" si="2"/>
         <v>252.17200000000003</v>
       </c>
-      <c r="I8" s="2">
-        <f t="shared" si="2"/>
+      <c r="I9">
+        <f t="shared" si="3"/>
         <v>254.64699999999999</v>
       </c>
-      <c r="J8" s="2">
-        <f t="shared" si="3"/>
+      <c r="J9">
+        <f t="shared" si="4"/>
         <v>255.79400000000001</v>
       </c>
-      <c r="K8" s="2">
-        <f t="shared" si="4"/>
+      <c r="K9">
+        <f t="shared" si="5"/>
         <v>259.62099999999998</v>
       </c>
-      <c r="L8" s="2">
-        <f t="shared" si="5"/>
+      <c r="L9">
+        <f t="shared" si="6"/>
         <v>263.84300000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>2016</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
         <v>2.9644328703703703E-3</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10" s="1">
         <v>2.9653472222222225E-3</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E10" s="1">
         <v>2.9826157407407405E-3</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F10" s="1">
         <v>3.0308449074074074E-3</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" s="1">
         <v>3.1190162037037037E-3</v>
       </c>
-      <c r="H9" s="2">
-        <f t="shared" si="1"/>
+      <c r="H10">
+        <f t="shared" si="2"/>
         <v>256.12700000000001</v>
       </c>
-      <c r="I9" s="2">
-        <f t="shared" si="2"/>
+      <c r="I10">
+        <f t="shared" si="3"/>
         <v>256.20600000000002</v>
       </c>
-      <c r="J9" s="2">
-        <f t="shared" si="3"/>
+      <c r="J10">
+        <f t="shared" si="4"/>
         <v>257.69799999999998</v>
       </c>
-      <c r="K9" s="2">
-        <f t="shared" si="4"/>
+      <c r="K10">
+        <f t="shared" si="5"/>
         <v>261.86500000000001</v>
       </c>
-      <c r="L9" s="2">
-        <f t="shared" si="5"/>
+      <c r="L10">
+        <f t="shared" si="6"/>
         <v>269.483</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A11">
         <v>2015</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1">
         <v>2.9654976851851852E-3</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>2.9766550925925924E-3</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>3.0009722222222221E-3</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3.0471296296296297E-3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>3.1259143518518519E-3</v>
       </c>
-      <c r="H10" s="2">
-        <f t="shared" si="1"/>
+      <c r="H11">
+        <f t="shared" si="2"/>
         <v>256.21899999999999</v>
       </c>
-      <c r="I10" s="2">
-        <f t="shared" si="2"/>
+      <c r="I11">
+        <f t="shared" si="3"/>
         <v>257.18299999999999</v>
       </c>
-      <c r="J10" s="2">
-        <f t="shared" si="3"/>
+      <c r="J11">
+        <f t="shared" si="4"/>
         <v>259.28399999999999</v>
       </c>
-      <c r="K10" s="2">
-        <f t="shared" si="4"/>
+      <c r="K11">
+        <f t="shared" si="5"/>
         <v>263.27199999999999</v>
       </c>
-      <c r="L10" s="2">
-        <f t="shared" si="5"/>
+      <c r="L11">
+        <f t="shared" si="6"/>
         <v>270.07900000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12">
         <v>2014</v>
       </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
         <v>3.0208680555555553E-3</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12" s="1">
         <v>3.0231828703703701E-3</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E12" s="1">
         <v>3.0308449074074074E-3</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12" s="1">
         <v>3.0521875000000002E-3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" s="1">
         <v>3.1064583333333335E-3</v>
       </c>
-      <c r="H11" s="2">
-        <f t="shared" si="1"/>
+      <c r="H12">
+        <f t="shared" si="2"/>
         <v>261.00299999999999</v>
       </c>
-      <c r="I11" s="2">
-        <f t="shared" si="2"/>
+      <c r="I12">
+        <f t="shared" si="3"/>
         <v>261.20299999999997</v>
       </c>
-      <c r="J11" s="2">
-        <f t="shared" si="3"/>
+      <c r="J12">
+        <f t="shared" si="4"/>
         <v>261.86500000000001</v>
       </c>
-      <c r="K11" s="2">
-        <f t="shared" si="4"/>
+      <c r="K12">
+        <f t="shared" si="5"/>
         <v>263.709</v>
       </c>
-      <c r="L11" s="2">
-        <f t="shared" si="5"/>
+      <c r="L12">
+        <f t="shared" si="6"/>
         <v>268.39800000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A13">
         <v>2013</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1">
         <v>2.9913888888888889E-3</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>3.0122685185185183E-3</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E13" s="1">
         <v>3.0385416666666664E-3</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13" s="1">
         <v>3.0639236111111114E-3</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="1">
         <v>3.1498611111111115E-3</v>
       </c>
-      <c r="H12" s="2">
-        <f t="shared" si="1"/>
+      <c r="H13">
+        <f t="shared" si="2"/>
         <v>258.45600000000002</v>
       </c>
-      <c r="I12" s="2">
-        <f t="shared" si="2"/>
+      <c r="I13">
+        <f t="shared" si="3"/>
         <v>260.26</v>
       </c>
-      <c r="J12" s="2">
-        <f t="shared" si="3"/>
+      <c r="J13">
+        <f t="shared" si="4"/>
         <v>262.52999999999997</v>
       </c>
-      <c r="K12" s="2">
-        <f t="shared" si="4"/>
+      <c r="K13">
+        <f t="shared" si="5"/>
         <v>264.72300000000001</v>
       </c>
-      <c r="L12" s="2">
-        <f t="shared" si="5"/>
+      <c r="L13">
+        <f t="shared" si="6"/>
         <v>272.14800000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A14">
         <v>2012</v>
       </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
         <v>2.930833333333333E-3</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="1">
         <v>2.9488773148148148E-3</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E14" s="1">
         <v>2.9635532407407406E-3</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>3.0478472222222222E-3</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <v>3.1454050925925924E-3</v>
       </c>
-      <c r="H13" s="2">
-        <f t="shared" si="1"/>
+      <c r="H14">
+        <f t="shared" si="2"/>
         <v>253.22399999999996</v>
       </c>
-      <c r="I13" s="2">
-        <f t="shared" si="2"/>
+      <c r="I14">
+        <f t="shared" si="3"/>
         <v>254.78299999999999</v>
       </c>
-      <c r="J13" s="2">
-        <f t="shared" si="3"/>
+      <c r="J14">
+        <f t="shared" si="4"/>
         <v>256.05099999999999</v>
       </c>
-      <c r="K13" s="2">
-        <f t="shared" si="4"/>
+      <c r="K14">
+        <f t="shared" si="5"/>
         <v>263.334</v>
       </c>
-      <c r="L13" s="2">
-        <f t="shared" si="5"/>
+      <c r="L14">
+        <f t="shared" si="6"/>
         <v>271.76299999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A15">
         <v>2011</v>
       </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
         <v>2.9799189814814814E-3</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D15" s="1">
         <v>3.0264004629629629E-3</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E15" s="1">
         <v>3.03962962962963E-3</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15" s="1">
         <v>3.1148263888888888E-3</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" s="1">
         <v>3.2004282407407407E-3</v>
       </c>
-      <c r="H14" s="2">
-        <f t="shared" si="1"/>
+      <c r="H15">
+        <f t="shared" si="2"/>
         <v>257.46499999999997</v>
       </c>
-      <c r="I14" s="2">
-        <f t="shared" si="2"/>
+      <c r="I15">
+        <f t="shared" si="3"/>
         <v>261.48099999999999</v>
       </c>
-      <c r="J14" s="2">
-        <f t="shared" si="3"/>
+      <c r="J15">
+        <f t="shared" si="4"/>
         <v>262.62400000000002</v>
       </c>
-      <c r="K14" s="2">
-        <f t="shared" si="4"/>
+      <c r="K15">
+        <f t="shared" si="5"/>
         <v>269.12099999999998</v>
       </c>
-      <c r="L14" s="2">
-        <f t="shared" si="5"/>
+      <c r="L15">
+        <f t="shared" si="6"/>
         <v>276.517</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A16">
         <v>2010</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1">
         <v>2.9628240740740739E-3</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="1">
         <v>2.9641435185185183E-3</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E16" s="1">
         <v>2.9764930555555551E-3</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16" s="1">
         <v>3.0351736111111109E-3</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16" s="1">
         <v>3.086539351851852E-3</v>
       </c>
-      <c r="H15" s="2">
-        <f t="shared" si="1"/>
+      <c r="H16">
+        <f t="shared" si="2"/>
         <v>255.98799999999997</v>
       </c>
-      <c r="I15" s="2">
-        <f t="shared" si="2"/>
+      <c r="I16">
+        <f t="shared" si="3"/>
         <v>256.10199999999998</v>
       </c>
-      <c r="J15" s="2">
-        <f t="shared" si="3"/>
+      <c r="J16">
+        <f t="shared" si="4"/>
         <v>257.16899999999998</v>
       </c>
-      <c r="K15" s="2">
-        <f t="shared" si="4"/>
+      <c r="K16">
+        <f t="shared" si="5"/>
         <v>262.23899999999998</v>
       </c>
-      <c r="L15" s="2">
-        <f t="shared" si="5"/>
+      <c r="L16">
+        <f t="shared" si="6"/>
         <v>266.67700000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>2009</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2.9532407407407407E-3</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2.979386574074074E-3</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2.9999652777777776E-3</v>
-      </c>
-      <c r="F16" s="1">
-        <v>3.0620833333333338E-3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>3.154618055555555E-3</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" si="1"/>
-        <v>255.16</v>
-      </c>
-      <c r="I16" s="2">
-        <f t="shared" si="2"/>
-        <v>257.41899999999998</v>
-      </c>
-      <c r="J16" s="2">
-        <f t="shared" si="3"/>
-        <v>259.197</v>
-      </c>
-      <c r="K16" s="2">
-        <f t="shared" si="4"/>
-        <v>264.56400000000002</v>
-      </c>
-      <c r="L16" s="2">
-        <f t="shared" si="5"/>
-        <v>272.55899999999997</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="1">
-        <v>2.9669328703703706E-3</v>
+        <v>2.9532407407407407E-3</v>
       </c>
       <c r="D17" s="1">
-        <v>2.9748148148148147E-3</v>
+        <v>2.979386574074074E-3</v>
       </c>
       <c r="E17" s="1">
-        <v>2.9889120370370373E-3</v>
+        <v>2.9999652777777776E-3</v>
       </c>
       <c r="F17" s="1">
-        <v>3.036550925925926E-3</v>
+        <v>3.0620833333333338E-3</v>
       </c>
       <c r="G17" s="1">
-        <v>3.0687731481481482E-3</v>
-      </c>
-      <c r="H17" s="2">
-        <f t="shared" si="1"/>
-        <v>256.34300000000002</v>
-      </c>
-      <c r="I17" s="2">
-        <f t="shared" si="2"/>
-        <v>257.024</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" si="3"/>
-        <v>258.24200000000002</v>
-      </c>
-      <c r="K17" s="2">
-        <f t="shared" si="4"/>
-        <v>262.358</v>
-      </c>
-      <c r="L17" s="2">
-        <f t="shared" si="5"/>
-        <v>265.142</v>
+        <v>3.154618055555555E-3</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>255.16</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>257.41899999999998</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="4"/>
+        <v>259.197</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="5"/>
+        <v>264.56400000000002</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="6"/>
+        <v>272.55899999999997</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="1">
-        <v>2.9626851851851854E-3</v>
+        <v>2.9669328703703706E-3</v>
       </c>
       <c r="D18" s="1">
-        <v>3.0148958333333334E-3</v>
+        <v>2.9748148148148147E-3</v>
       </c>
       <c r="E18" s="1">
-        <v>3.0150578703703702E-3</v>
+        <v>2.9889120370370373E-3</v>
       </c>
       <c r="F18" s="1">
-        <v>3.0855902777777782E-3</v>
+        <v>3.036550925925926E-3</v>
       </c>
       <c r="G18" s="1">
-        <v>3.1264467592592594E-3</v>
-      </c>
-      <c r="H18" s="2">
-        <f t="shared" si="1"/>
-        <v>255.97600000000003</v>
-      </c>
-      <c r="I18" s="2">
-        <f t="shared" si="2"/>
-        <v>260.48700000000002</v>
-      </c>
-      <c r="J18" s="2">
-        <f t="shared" si="3"/>
-        <v>260.50099999999998</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="4"/>
-        <v>266.59500000000003</v>
-      </c>
-      <c r="L18" s="2">
-        <f t="shared" si="5"/>
-        <v>270.125</v>
+        <v>3.0687731481481482E-3</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>256.34300000000002</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="3"/>
+        <v>257.024</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="4"/>
+        <v>258.24200000000002</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="5"/>
+        <v>262.358</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="6"/>
+        <v>265.142</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>3.0453125000000003E-3</v>
+        <v>2.9626851851851854E-3</v>
       </c>
       <c r="D19" s="1">
-        <v>3.056076388888889E-3</v>
+        <v>3.0148958333333334E-3</v>
       </c>
       <c r="E19" s="1">
-        <v>3.0578472222222218E-3</v>
+        <v>3.0150578703703702E-3</v>
       </c>
       <c r="F19" s="1">
-        <v>3.0907638888888894E-3</v>
+        <v>3.0855902777777782E-3</v>
       </c>
       <c r="G19" s="1">
-        <v>3.1762037037037037E-3</v>
-      </c>
-      <c r="H19" s="2">
-        <f t="shared" si="1"/>
-        <v>263.11500000000001</v>
-      </c>
-      <c r="I19" s="2">
-        <f t="shared" si="2"/>
-        <v>264.04500000000002</v>
-      </c>
-      <c r="J19" s="2">
-        <f t="shared" si="3"/>
-        <v>264.19799999999998</v>
-      </c>
-      <c r="K19" s="2">
-        <f t="shared" si="4"/>
-        <v>267.04200000000003</v>
-      </c>
-      <c r="L19" s="2">
-        <f t="shared" si="5"/>
-        <v>274.42399999999998</v>
+        <v>3.1264467592592594E-3</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>255.97600000000003</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>260.48700000000002</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="4"/>
+        <v>260.50099999999998</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="5"/>
+        <v>266.59500000000003</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="6"/>
+        <v>270.125</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="1">
-        <v>3.0764699074074075E-3</v>
+        <v>3.0453125000000003E-3</v>
       </c>
       <c r="D20" s="1">
-        <v>3.1117824074074073E-3</v>
+        <v>3.056076388888889E-3</v>
       </c>
       <c r="E20" s="1">
-        <v>3.1127662037037035E-3</v>
+        <v>3.0578472222222218E-3</v>
       </c>
       <c r="F20" s="1">
-        <v>3.1498379629629632E-3</v>
+        <v>3.0907638888888894E-3</v>
       </c>
       <c r="G20" s="1">
-        <v>3.2679513888888888E-3</v>
-      </c>
-      <c r="H20" s="2">
-        <f t="shared" si="1"/>
-        <v>265.80700000000002</v>
-      </c>
-      <c r="I20" s="2">
-        <f t="shared" si="2"/>
-        <v>268.858</v>
-      </c>
-      <c r="J20" s="2">
-        <f t="shared" si="3"/>
-        <v>268.94299999999998</v>
-      </c>
-      <c r="K20" s="2">
-        <f t="shared" si="4"/>
-        <v>272.14600000000002</v>
-      </c>
-      <c r="L20" s="2">
-        <f t="shared" si="5"/>
-        <v>282.351</v>
+        <v>3.1762037037037037E-3</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>263.11500000000001</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>264.04500000000002</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="4"/>
+        <v>264.19799999999998</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="5"/>
+        <v>267.04200000000003</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="6"/>
+        <v>274.42399999999998</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="1">
-        <v>3.0054513888888887E-3</v>
+        <v>3.0764699074074075E-3</v>
       </c>
       <c r="D21" s="1">
-        <v>3.0269675925925924E-3</v>
+        <v>3.1117824074074073E-3</v>
       </c>
       <c r="E21" s="1">
-        <v>3.0313888888888886E-3</v>
+        <v>3.1127662037037035E-3</v>
       </c>
       <c r="F21" s="1">
-        <v>3.0745138888888888E-3</v>
+        <v>3.1498379629629632E-3</v>
       </c>
       <c r="G21" s="1">
-        <v>3.1596064814814816E-3</v>
-      </c>
-      <c r="H21" s="2">
-        <f t="shared" si="1"/>
-        <v>259.67099999999999</v>
-      </c>
-      <c r="I21" s="2">
-        <f t="shared" si="2"/>
-        <v>261.52999999999997</v>
-      </c>
-      <c r="J21" s="2">
-        <f t="shared" si="3"/>
-        <v>261.91199999999998</v>
-      </c>
-      <c r="K21" s="2">
-        <f t="shared" si="4"/>
-        <v>265.63799999999998</v>
-      </c>
-      <c r="L21" s="2">
-        <f t="shared" si="5"/>
-        <v>272.99</v>
+        <v>3.2679513888888888E-3</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>265.80700000000002</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>268.858</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="4"/>
+        <v>268.94299999999998</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="5"/>
+        <v>272.14600000000002</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="6"/>
+        <v>282.351</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="1">
-        <v>2.9784953703703701E-3</v>
+        <v>3.0054513888888887E-3</v>
       </c>
       <c r="D22" s="1">
-        <v>3.0303472222222225E-3</v>
+        <v>3.0269675925925924E-3</v>
       </c>
       <c r="E22" s="1">
-        <v>3.0317245370370368E-3</v>
+        <v>3.0313888888888886E-3</v>
       </c>
       <c r="F22" s="1">
-        <v>3.0813425925925926E-3</v>
+        <v>3.0745138888888888E-3</v>
       </c>
       <c r="G22" s="1">
-        <v>3.1530439814814815E-3</v>
-      </c>
-      <c r="H22" s="2">
-        <f t="shared" si="1"/>
-        <v>257.34199999999998</v>
-      </c>
-      <c r="I22" s="2">
-        <f t="shared" si="2"/>
-        <v>261.822</v>
-      </c>
-      <c r="J22" s="2">
-        <f t="shared" si="3"/>
-        <v>261.94099999999997</v>
-      </c>
-      <c r="K22" s="2">
-        <f t="shared" si="4"/>
-        <v>266.22800000000001</v>
-      </c>
-      <c r="L22" s="2">
-        <f t="shared" si="5"/>
-        <v>272.423</v>
+        <v>3.1596064814814816E-3</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>259.67099999999999</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>261.52999999999997</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="4"/>
+        <v>261.91199999999998</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="5"/>
+        <v>265.63799999999998</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="6"/>
+        <v>272.99</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="1">
-        <v>3.001041666666667E-3</v>
+        <v>2.9784953703703701E-3</v>
       </c>
       <c r="D23" s="1">
-        <v>3.0223495370370365E-3</v>
+        <v>3.0303472222222225E-3</v>
       </c>
       <c r="E23" s="1">
-        <v>3.037835648148148E-3</v>
+        <v>3.0317245370370368E-3</v>
       </c>
       <c r="F23" s="1">
-        <v>3.0830902777777779E-3</v>
+        <v>3.0813425925925926E-3</v>
       </c>
       <c r="G23" s="1">
-        <v>3.1568518518518521E-3</v>
-      </c>
-      <c r="H23" s="2">
-        <f t="shared" si="1"/>
-        <v>259.29000000000002</v>
-      </c>
-      <c r="I23" s="2">
-        <f t="shared" si="2"/>
-        <v>261.13099999999997</v>
-      </c>
-      <c r="J23" s="2">
-        <f t="shared" si="3"/>
-        <v>262.46899999999999</v>
-      </c>
-      <c r="K23" s="2">
-        <f t="shared" si="4"/>
-        <v>266.37900000000002</v>
-      </c>
-      <c r="L23" s="2">
-        <f t="shared" si="5"/>
-        <v>272.75200000000001</v>
+        <v>3.1530439814814815E-3</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>257.34199999999998</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="3"/>
+        <v>261.822</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="4"/>
+        <v>261.94099999999997</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="5"/>
+        <v>266.22800000000001</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="6"/>
+        <v>272.423</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="1">
-        <v>3.079837962962963E-3</v>
+        <v>3.001041666666667E-3</v>
       </c>
       <c r="D24" s="1">
-        <v>3.0996180555555555E-3</v>
+        <v>3.0223495370370365E-3</v>
       </c>
       <c r="E24" s="1">
-        <v>3.1477893518518517E-3</v>
+        <v>3.037835648148148E-3</v>
       </c>
       <c r="F24" s="1">
-        <v>3.1896759259259261E-3</v>
+        <v>3.0830902777777779E-3</v>
       </c>
       <c r="G24" s="1">
-        <v>3.231701388888889E-3</v>
-      </c>
-      <c r="H24" s="2">
-        <f t="shared" si="1"/>
-        <v>266.09800000000001</v>
-      </c>
-      <c r="I24" s="2">
-        <f t="shared" si="2"/>
-        <v>267.80700000000002</v>
-      </c>
-      <c r="J24" s="2">
-        <f t="shared" si="3"/>
-        <v>271.96899999999999</v>
-      </c>
-      <c r="K24" s="2">
-        <f t="shared" si="4"/>
-        <v>275.58800000000002</v>
-      </c>
-      <c r="L24" s="2">
-        <f t="shared" si="5"/>
-        <v>279.21899999999999</v>
+        <v>3.1568518518518521E-3</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>259.29000000000002</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="3"/>
+        <v>261.13099999999997</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="4"/>
+        <v>262.46899999999999</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="5"/>
+        <v>266.37900000000002</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="6"/>
+        <v>272.75200000000001</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25">
+        <v>2001</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3.079837962962963E-3</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3.0996180555555555E-3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3.1477893518518517E-3</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3.1896759259259261E-3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3.231701388888889E-3</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="2"/>
+        <v>266.09800000000001</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>267.80700000000002</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="4"/>
+        <v>271.96899999999999</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="5"/>
+        <v>275.58800000000002</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="6"/>
+        <v>279.21899999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26">
         <v>2000</v>
       </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
         <v>3.0448958333333335E-3</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>3.0559722222222221E-3</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E26" s="1">
         <v>3.0654166666666664E-3</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="1">
         <v>3.1504050925925927E-3</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="2">
-        <f t="shared" si="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26">
+        <f t="shared" si="2"/>
         <v>263.07900000000001</v>
       </c>
-      <c r="I25" s="2">
-        <f t="shared" si="2"/>
+      <c r="I26">
+        <f t="shared" si="3"/>
         <v>264.036</v>
       </c>
-      <c r="J25" s="2">
-        <f t="shared" si="3"/>
+      <c r="J26">
+        <f t="shared" si="4"/>
         <v>264.85199999999998</v>
       </c>
-      <c r="K25" s="2">
-        <f t="shared" si="4"/>
+      <c r="K26">
+        <f t="shared" si="5"/>
         <v>272.19499999999999</v>
       </c>
-      <c r="L25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Medals_Men_IP.xlsx
+++ b/pages/WR_progressions/Medals_Men_IP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A2C5EB-D1A4-4156-9198-2BDA9A907A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76EFFD5-A57B-407B-B7C6-F4139286BAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
+    <workbookView xWindow="25490" yWindow="10800" windowWidth="19420" windowHeight="10300" xr2:uid="{CC4DF8B1-FDE8-46DE-898D-C50D7CB0E2AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
   <si>
     <t>8th</t>
   </si>
@@ -453,13 +453,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1400477D-CA59-426F-9BF4-08585135C868}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.06640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
@@ -506,1079 +506,1116 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <f>H2/86400</f>
-        <v>2.769722222222222E-3</v>
+        <v>2.8106944444444442E-3</v>
       </c>
       <c r="D2" s="1">
-        <f t="shared" ref="D2:G2" si="0">I2/86400</f>
-        <v>2.7812037037037037E-3</v>
+        <f t="shared" ref="D2" si="0">I2/86400</f>
+        <v>2.8367129629629632E-3</v>
       </c>
       <c r="E2" s="1">
-        <f t="shared" si="0"/>
-        <v>2.7971180555555553E-3</v>
+        <f t="shared" ref="E2" si="1">J2/86400</f>
+        <v>2.8465740740740739E-3</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" si="0"/>
-        <v>2.8775810185185185E-3</v>
+        <f t="shared" ref="F2" si="2">K2/86400</f>
+        <v>2.8785532407407406E-3</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" si="0"/>
-        <v>2.9595023148148145E-3</v>
-      </c>
-      <c r="H2">
-        <v>239.304</v>
-      </c>
-      <c r="I2">
-        <v>240.29599999999999</v>
-      </c>
-      <c r="J2">
-        <v>241.67099999999999</v>
+        <f t="shared" ref="G2" si="3">L2/86400</f>
+        <v>2.9870486111111113E-3</v>
+      </c>
+      <c r="H2" s="2">
+        <v>242.84399999999999</v>
+      </c>
+      <c r="I2" s="2">
+        <v>245.09200000000001</v>
+      </c>
+      <c r="J2" s="2">
+        <v>245.94399999999999</v>
       </c>
       <c r="K2" s="2">
-        <v>248.62299999999999</v>
+        <v>248.70699999999999</v>
       </c>
       <c r="L2" s="2">
-        <v>255.70099999999999</v>
+        <v>258.08100000000002</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>2.7933333333333334E-3</v>
+        <f>H3/86400</f>
+        <v>2.769722222222222E-3</v>
       </c>
       <c r="D3" s="1">
-        <v>2.8120486111111111E-3</v>
+        <f t="shared" ref="D3:G3" si="4">I3/86400</f>
+        <v>2.7812037037037037E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>2.8517708333333333E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.7971180555555553E-3</v>
       </c>
       <c r="F3" s="1">
-        <v>2.891203703703704E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.8775810185185185E-3</v>
       </c>
       <c r="G3" s="1">
-        <v>2.9494212962962963E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.9595023148148145E-3</v>
       </c>
       <c r="H3">
-        <f>86400*C3</f>
-        <v>241.34400000000002</v>
+        <v>239.304</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:L3" si="1">86400*D3</f>
-        <v>242.96099999999998</v>
+        <v>240.29599999999999</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
-        <v>246.393</v>
-      </c>
-      <c r="K3">
-        <f t="shared" si="1"/>
-        <v>249.8</v>
-      </c>
-      <c r="L3">
-        <f t="shared" si="1"/>
-        <v>254.83</v>
+        <v>241.67099999999999</v>
+      </c>
+      <c r="K3" s="2">
+        <v>248.62299999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>255.70099999999999</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>2.7857986111111113E-3</v>
+        <v>2.7933333333333334E-3</v>
       </c>
       <c r="D4" s="1">
-        <v>2.8126388888888888E-3</v>
+        <v>2.8120486111111111E-3</v>
       </c>
       <c r="E4" s="1">
-        <v>2.8377430555555556E-3</v>
+        <v>2.8517708333333333E-3</v>
       </c>
       <c r="F4" s="1">
-        <v>2.8889699074074074E-3</v>
+        <v>2.891203703703704E-3</v>
       </c>
       <c r="G4" s="1">
-        <v>2.9803125000000003E-3</v>
+        <v>2.9494212962962963E-3</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H26" si="2">86400*C4</f>
-        <v>240.69300000000001</v>
+        <f>86400*C4</f>
+        <v>241.34400000000002</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I26" si="3">86400*D4</f>
-        <v>243.012</v>
+        <f t="shared" ref="I4:L4" si="5">86400*D4</f>
+        <v>242.96099999999998</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J26" si="4">86400*E4</f>
-        <v>245.18100000000001</v>
+        <f t="shared" si="5"/>
+        <v>246.393</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K26" si="5">86400*F4</f>
-        <v>249.607</v>
+        <f t="shared" si="5"/>
+        <v>249.8</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L4:L25" si="6">86400*G4</f>
-        <v>257.49900000000002</v>
+        <f t="shared" si="5"/>
+        <v>254.83</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>2.8152430555555556E-3</v>
+        <v>2.7857986111111113E-3</v>
       </c>
       <c r="D5" s="1">
-        <v>2.8447337962962962E-3</v>
+        <v>2.8126388888888888E-3</v>
       </c>
       <c r="E5" s="1">
-        <v>2.8518749999999998E-3</v>
+        <v>2.8377430555555556E-3</v>
       </c>
       <c r="F5" s="1">
-        <v>2.937962962962963E-3</v>
+        <v>2.8889699074074074E-3</v>
       </c>
       <c r="G5" s="1">
-        <v>3.0406944444444444E-3</v>
+        <v>2.9803125000000003E-3</v>
       </c>
       <c r="H5">
-        <f t="shared" si="2"/>
-        <v>243.23699999999999</v>
+        <f t="shared" ref="H5:H27" si="6">86400*C5</f>
+        <v>240.69300000000001</v>
       </c>
       <c r="I5">
-        <f t="shared" si="3"/>
-        <v>245.785</v>
+        <f t="shared" ref="I5:I27" si="7">86400*D5</f>
+        <v>243.012</v>
       </c>
       <c r="J5">
-        <f t="shared" si="4"/>
-        <v>246.40199999999999</v>
+        <f t="shared" ref="J5:J27" si="8">86400*E5</f>
+        <v>245.18100000000001</v>
       </c>
       <c r="K5">
-        <f t="shared" si="5"/>
-        <v>253.84</v>
+        <f t="shared" ref="K5:K27" si="9">86400*F5</f>
+        <v>249.607</v>
       </c>
       <c r="L5">
-        <f t="shared" si="6"/>
-        <v>262.71600000000001</v>
+        <f t="shared" ref="L5:L26" si="10">86400*G5</f>
+        <v>257.49900000000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>2.8001620370370372E-3</v>
+        <v>2.8152430555555556E-3</v>
       </c>
       <c r="D6" s="1">
-        <v>2.8199074074074073E-3</v>
+        <v>2.8447337962962962E-3</v>
       </c>
       <c r="E6" s="1">
-        <v>2.8656597222222221E-3</v>
+        <v>2.8518749999999998E-3</v>
       </c>
       <c r="F6" s="1">
-        <v>2.9031134259259262E-3</v>
+        <v>2.937962962962963E-3</v>
       </c>
       <c r="G6" s="1">
-        <v>3.0261805555555554E-3</v>
+        <v>3.0406944444444444E-3</v>
       </c>
       <c r="H6">
-        <f t="shared" si="2"/>
-        <v>241.93400000000003</v>
+        <f t="shared" si="6"/>
+        <v>243.23699999999999</v>
       </c>
       <c r="I6">
-        <f t="shared" si="3"/>
-        <v>243.64</v>
+        <f t="shared" si="7"/>
+        <v>245.785</v>
       </c>
       <c r="J6">
-        <f t="shared" si="4"/>
-        <v>247.59299999999999</v>
+        <f t="shared" si="8"/>
+        <v>246.40199999999999</v>
       </c>
       <c r="K6">
-        <f t="shared" si="5"/>
-        <v>250.82900000000001</v>
+        <f t="shared" si="9"/>
+        <v>253.84</v>
       </c>
       <c r="L6">
-        <f t="shared" si="6"/>
-        <v>261.46199999999999</v>
-      </c>
-      <c r="N6">
-        <v>239.304</v>
+        <f t="shared" si="10"/>
+        <v>262.71600000000001</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>2.864074074074074E-3</v>
+        <v>2.8001620370370372E-3</v>
       </c>
       <c r="D7" s="1">
-        <v>2.8829976851851855E-3</v>
+        <v>2.8199074074074073E-3</v>
       </c>
       <c r="E7" s="1">
-        <v>2.9139351851851852E-3</v>
+        <v>2.8656597222222221E-3</v>
       </c>
       <c r="F7" s="1">
-        <v>2.969710648148148E-3</v>
+        <v>2.9031134259259262E-3</v>
       </c>
       <c r="G7" s="1">
-        <v>3.0736342592592595E-3</v>
+        <v>3.0261805555555554E-3</v>
       </c>
       <c r="H7">
-        <f t="shared" si="2"/>
-        <v>247.45599999999999</v>
+        <f t="shared" si="6"/>
+        <v>241.93400000000003</v>
       </c>
       <c r="I7">
-        <f t="shared" si="3"/>
-        <v>249.09100000000004</v>
+        <f t="shared" si="7"/>
+        <v>243.64</v>
       </c>
       <c r="J7">
-        <f t="shared" si="4"/>
-        <v>251.76400000000001</v>
+        <f t="shared" si="8"/>
+        <v>247.59299999999999</v>
       </c>
       <c r="K7">
-        <f t="shared" si="5"/>
-        <v>256.58299999999997</v>
+        <f t="shared" si="9"/>
+        <v>250.82900000000001</v>
       </c>
       <c r="L7">
-        <f t="shared" si="6"/>
-        <v>265.56200000000001</v>
-      </c>
-      <c r="N7">
-        <v>240.29599999999999</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>261.46199999999999</v>
+      </c>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>2.9208912037037038E-3</v>
+        <v>2.864074074074074E-3</v>
       </c>
       <c r="D8" s="1">
-        <v>2.9354398148148148E-3</v>
+        <v>2.8829976851851855E-3</v>
       </c>
       <c r="E8" s="1">
-        <v>2.9401041666666668E-3</v>
+        <v>2.9139351851851852E-3</v>
       </c>
       <c r="F8" s="1">
-        <v>3.013935185185185E-3</v>
+        <v>2.969710648148148E-3</v>
       </c>
       <c r="G8" s="1">
-        <v>3.0857175925925926E-3</v>
+        <v>3.0736342592592595E-3</v>
       </c>
       <c r="H8">
-        <f t="shared" si="2"/>
-        <v>252.36500000000001</v>
+        <f t="shared" si="6"/>
+        <v>247.45599999999999</v>
       </c>
       <c r="I8">
-        <f t="shared" si="3"/>
-        <v>253.62199999999999</v>
+        <f t="shared" si="7"/>
+        <v>249.09100000000004</v>
       </c>
       <c r="J8">
-        <f t="shared" si="4"/>
-        <v>254.02500000000001</v>
+        <f t="shared" si="8"/>
+        <v>251.76400000000001</v>
       </c>
       <c r="K8">
-        <f t="shared" si="5"/>
-        <v>260.404</v>
+        <f t="shared" si="9"/>
+        <v>256.58299999999997</v>
       </c>
       <c r="L8">
-        <f t="shared" si="6"/>
-        <v>266.60599999999999</v>
-      </c>
-      <c r="N8">
-        <v>241.67099999999999</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>265.56200000000001</v>
+      </c>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="1">
-        <v>2.9186574074074076E-3</v>
+        <v>2.9208912037037038E-3</v>
       </c>
       <c r="D9" s="1">
-        <v>2.9473032407407408E-3</v>
+        <v>2.9354398148148148E-3</v>
       </c>
       <c r="E9" s="1">
-        <v>2.960578703703704E-3</v>
+        <v>2.9401041666666668E-3</v>
       </c>
       <c r="F9" s="1">
-        <v>3.0048726851851851E-3</v>
+        <v>3.013935185185185E-3</v>
       </c>
       <c r="G9" s="1">
-        <v>3.0537384259259263E-3</v>
+        <v>3.0857175925925926E-3</v>
       </c>
       <c r="H9">
-        <f t="shared" si="2"/>
-        <v>252.17200000000003</v>
+        <f t="shared" si="6"/>
+        <v>252.36500000000001</v>
       </c>
       <c r="I9">
-        <f t="shared" si="3"/>
-        <v>254.64699999999999</v>
+        <f t="shared" si="7"/>
+        <v>253.62199999999999</v>
       </c>
       <c r="J9">
-        <f t="shared" si="4"/>
-        <v>255.79400000000001</v>
+        <f t="shared" si="8"/>
+        <v>254.02500000000001</v>
       </c>
       <c r="K9">
-        <f t="shared" si="5"/>
-        <v>259.62099999999998</v>
+        <f t="shared" si="9"/>
+        <v>260.404</v>
       </c>
       <c r="L9">
-        <f t="shared" si="6"/>
-        <v>263.84300000000002</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>266.60599999999999</v>
+      </c>
+      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="1">
-        <v>2.9644328703703703E-3</v>
+        <v>2.9186574074074076E-3</v>
       </c>
       <c r="D10" s="1">
-        <v>2.9653472222222225E-3</v>
+        <v>2.9473032407407408E-3</v>
       </c>
       <c r="E10" s="1">
-        <v>2.9826157407407405E-3</v>
+        <v>2.960578703703704E-3</v>
       </c>
       <c r="F10" s="1">
-        <v>3.0308449074074074E-3</v>
+        <v>3.0048726851851851E-3</v>
       </c>
       <c r="G10" s="1">
-        <v>3.1190162037037037E-3</v>
+        <v>3.0537384259259263E-3</v>
       </c>
       <c r="H10">
-        <f t="shared" si="2"/>
-        <v>256.12700000000001</v>
+        <f t="shared" si="6"/>
+        <v>252.17200000000003</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
-        <v>256.20600000000002</v>
+        <f t="shared" si="7"/>
+        <v>254.64699999999999</v>
       </c>
       <c r="J10">
-        <f t="shared" si="4"/>
-        <v>257.69799999999998</v>
+        <f t="shared" si="8"/>
+        <v>255.79400000000001</v>
       </c>
       <c r="K10">
-        <f t="shared" si="5"/>
-        <v>261.86500000000001</v>
+        <f t="shared" si="9"/>
+        <v>259.62099999999998</v>
       </c>
       <c r="L10">
-        <f t="shared" si="6"/>
-        <v>269.483</v>
+        <f t="shared" si="10"/>
+        <v>263.84300000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="1">
-        <v>2.9654976851851852E-3</v>
+        <v>2.9644328703703703E-3</v>
       </c>
       <c r="D11" s="1">
-        <v>2.9766550925925924E-3</v>
+        <v>2.9653472222222225E-3</v>
       </c>
       <c r="E11" s="1">
-        <v>3.0009722222222221E-3</v>
+        <v>2.9826157407407405E-3</v>
       </c>
       <c r="F11" s="1">
-        <v>3.0471296296296297E-3</v>
+        <v>3.0308449074074074E-3</v>
       </c>
       <c r="G11" s="1">
-        <v>3.1259143518518519E-3</v>
+        <v>3.1190162037037037E-3</v>
       </c>
       <c r="H11">
-        <f t="shared" si="2"/>
-        <v>256.21899999999999</v>
+        <f t="shared" si="6"/>
+        <v>256.12700000000001</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
-        <v>257.18299999999999</v>
+        <f t="shared" si="7"/>
+        <v>256.20600000000002</v>
       </c>
       <c r="J11">
-        <f t="shared" si="4"/>
-        <v>259.28399999999999</v>
+        <f t="shared" si="8"/>
+        <v>257.69799999999998</v>
       </c>
       <c r="K11">
-        <f t="shared" si="5"/>
-        <v>263.27199999999999</v>
+        <f t="shared" si="9"/>
+        <v>261.86500000000001</v>
       </c>
       <c r="L11">
-        <f t="shared" si="6"/>
-        <v>270.07900000000001</v>
+        <f t="shared" si="10"/>
+        <v>269.483</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>3.0208680555555553E-3</v>
+        <v>2.9654976851851852E-3</v>
       </c>
       <c r="D12" s="1">
-        <v>3.0231828703703701E-3</v>
+        <v>2.9766550925925924E-3</v>
       </c>
       <c r="E12" s="1">
-        <v>3.0308449074074074E-3</v>
+        <v>3.0009722222222221E-3</v>
       </c>
       <c r="F12" s="1">
-        <v>3.0521875000000002E-3</v>
+        <v>3.0471296296296297E-3</v>
       </c>
       <c r="G12" s="1">
-        <v>3.1064583333333335E-3</v>
+        <v>3.1259143518518519E-3</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
-        <v>261.00299999999999</v>
+        <f t="shared" si="6"/>
+        <v>256.21899999999999</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
-        <v>261.20299999999997</v>
+        <f t="shared" si="7"/>
+        <v>257.18299999999999</v>
       </c>
       <c r="J12">
-        <f t="shared" si="4"/>
-        <v>261.86500000000001</v>
+        <f t="shared" si="8"/>
+        <v>259.28399999999999</v>
       </c>
       <c r="K12">
-        <f t="shared" si="5"/>
-        <v>263.709</v>
+        <f t="shared" si="9"/>
+        <v>263.27199999999999</v>
       </c>
       <c r="L12">
-        <f t="shared" si="6"/>
-        <v>268.39800000000002</v>
+        <f t="shared" si="10"/>
+        <v>270.07900000000001</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="1">
-        <v>2.9913888888888889E-3</v>
+        <v>3.0208680555555553E-3</v>
       </c>
       <c r="D13" s="1">
-        <v>3.0122685185185183E-3</v>
+        <v>3.0231828703703701E-3</v>
       </c>
       <c r="E13" s="1">
-        <v>3.0385416666666664E-3</v>
+        <v>3.0308449074074074E-3</v>
       </c>
       <c r="F13" s="1">
-        <v>3.0639236111111114E-3</v>
+        <v>3.0521875000000002E-3</v>
       </c>
       <c r="G13" s="1">
-        <v>3.1498611111111115E-3</v>
+        <v>3.1064583333333335E-3</v>
       </c>
       <c r="H13">
-        <f t="shared" si="2"/>
-        <v>258.45600000000002</v>
+        <f t="shared" si="6"/>
+        <v>261.00299999999999</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
-        <v>260.26</v>
+        <f t="shared" si="7"/>
+        <v>261.20299999999997</v>
       </c>
       <c r="J13">
-        <f t="shared" si="4"/>
-        <v>262.52999999999997</v>
+        <f t="shared" si="8"/>
+        <v>261.86500000000001</v>
       </c>
       <c r="K13">
-        <f t="shared" si="5"/>
-        <v>264.72300000000001</v>
+        <f t="shared" si="9"/>
+        <v>263.709</v>
       </c>
       <c r="L13">
-        <f t="shared" si="6"/>
-        <v>272.14800000000002</v>
+        <f t="shared" si="10"/>
+        <v>268.39800000000002</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="1">
-        <v>2.930833333333333E-3</v>
+        <v>2.9913888888888889E-3</v>
       </c>
       <c r="D14" s="1">
-        <v>2.9488773148148148E-3</v>
+        <v>3.0122685185185183E-3</v>
       </c>
       <c r="E14" s="1">
-        <v>2.9635532407407406E-3</v>
+        <v>3.0385416666666664E-3</v>
       </c>
       <c r="F14" s="1">
-        <v>3.0478472222222222E-3</v>
+        <v>3.0639236111111114E-3</v>
       </c>
       <c r="G14" s="1">
-        <v>3.1454050925925924E-3</v>
+        <v>3.1498611111111115E-3</v>
       </c>
       <c r="H14">
-        <f t="shared" si="2"/>
-        <v>253.22399999999996</v>
+        <f t="shared" si="6"/>
+        <v>258.45600000000002</v>
       </c>
       <c r="I14">
-        <f t="shared" si="3"/>
-        <v>254.78299999999999</v>
+        <f t="shared" si="7"/>
+        <v>260.26</v>
       </c>
       <c r="J14">
-        <f t="shared" si="4"/>
-        <v>256.05099999999999</v>
+        <f t="shared" si="8"/>
+        <v>262.52999999999997</v>
       </c>
       <c r="K14">
-        <f t="shared" si="5"/>
-        <v>263.334</v>
+        <f t="shared" si="9"/>
+        <v>264.72300000000001</v>
       </c>
       <c r="L14">
-        <f t="shared" si="6"/>
-        <v>271.76299999999998</v>
+        <f t="shared" si="10"/>
+        <v>272.14800000000002</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="1">
-        <v>2.9799189814814814E-3</v>
+        <v>2.930833333333333E-3</v>
       </c>
       <c r="D15" s="1">
-        <v>3.0264004629629629E-3</v>
+        <v>2.9488773148148148E-3</v>
       </c>
       <c r="E15" s="1">
-        <v>3.03962962962963E-3</v>
+        <v>2.9635532407407406E-3</v>
       </c>
       <c r="F15" s="1">
-        <v>3.1148263888888888E-3</v>
+        <v>3.0478472222222222E-3</v>
       </c>
       <c r="G15" s="1">
-        <v>3.2004282407407407E-3</v>
+        <v>3.1454050925925924E-3</v>
       </c>
       <c r="H15">
-        <f t="shared" si="2"/>
-        <v>257.46499999999997</v>
+        <f t="shared" si="6"/>
+        <v>253.22399999999996</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
-        <v>261.48099999999999</v>
+        <f t="shared" si="7"/>
+        <v>254.78299999999999</v>
       </c>
       <c r="J15">
-        <f t="shared" si="4"/>
-        <v>262.62400000000002</v>
+        <f t="shared" si="8"/>
+        <v>256.05099999999999</v>
       </c>
       <c r="K15">
-        <f t="shared" si="5"/>
-        <v>269.12099999999998</v>
+        <f t="shared" si="9"/>
+        <v>263.334</v>
       </c>
       <c r="L15">
-        <f t="shared" si="6"/>
-        <v>276.517</v>
+        <f t="shared" si="10"/>
+        <v>271.76299999999998</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="1">
-        <v>2.9628240740740739E-3</v>
+        <v>2.9799189814814814E-3</v>
       </c>
       <c r="D16" s="1">
-        <v>2.9641435185185183E-3</v>
+        <v>3.0264004629629629E-3</v>
       </c>
       <c r="E16" s="1">
-        <v>2.9764930555555551E-3</v>
+        <v>3.03962962962963E-3</v>
       </c>
       <c r="F16" s="1">
-        <v>3.0351736111111109E-3</v>
+        <v>3.1148263888888888E-3</v>
       </c>
       <c r="G16" s="1">
-        <v>3.086539351851852E-3</v>
+        <v>3.2004282407407407E-3</v>
       </c>
       <c r="H16">
-        <f t="shared" si="2"/>
-        <v>255.98799999999997</v>
+        <f t="shared" si="6"/>
+        <v>257.46499999999997</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
-        <v>256.10199999999998</v>
+        <f t="shared" si="7"/>
+        <v>261.48099999999999</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
-        <v>257.16899999999998</v>
+        <f t="shared" si="8"/>
+        <v>262.62400000000002</v>
       </c>
       <c r="K16">
-        <f t="shared" si="5"/>
-        <v>262.23899999999998</v>
+        <f t="shared" si="9"/>
+        <v>269.12099999999998</v>
       </c>
       <c r="L16">
-        <f t="shared" si="6"/>
-        <v>266.67700000000002</v>
+        <f t="shared" si="10"/>
+        <v>276.517</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="1">
-        <v>2.9532407407407407E-3</v>
+        <v>2.9628240740740739E-3</v>
       </c>
       <c r="D17" s="1">
-        <v>2.979386574074074E-3</v>
+        <v>2.9641435185185183E-3</v>
       </c>
       <c r="E17" s="1">
-        <v>2.9999652777777776E-3</v>
+        <v>2.9764930555555551E-3</v>
       </c>
       <c r="F17" s="1">
-        <v>3.0620833333333338E-3</v>
+        <v>3.0351736111111109E-3</v>
       </c>
       <c r="G17" s="1">
-        <v>3.154618055555555E-3</v>
+        <v>3.086539351851852E-3</v>
       </c>
       <c r="H17">
-        <f t="shared" si="2"/>
-        <v>255.16</v>
+        <f t="shared" si="6"/>
+        <v>255.98799999999997</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
-        <v>257.41899999999998</v>
+        <f t="shared" si="7"/>
+        <v>256.10199999999998</v>
       </c>
       <c r="J17">
-        <f t="shared" si="4"/>
-        <v>259.197</v>
+        <f t="shared" si="8"/>
+        <v>257.16899999999998</v>
       </c>
       <c r="K17">
-        <f t="shared" si="5"/>
-        <v>264.56400000000002</v>
+        <f t="shared" si="9"/>
+        <v>262.23899999999998</v>
       </c>
       <c r="L17">
-        <f t="shared" si="6"/>
-        <v>272.55899999999997</v>
+        <f t="shared" si="10"/>
+        <v>266.67700000000002</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="1">
-        <v>2.9669328703703706E-3</v>
+        <v>2.9532407407407407E-3</v>
       </c>
       <c r="D18" s="1">
-        <v>2.9748148148148147E-3</v>
+        <v>2.979386574074074E-3</v>
       </c>
       <c r="E18" s="1">
-        <v>2.9889120370370373E-3</v>
+        <v>2.9999652777777776E-3</v>
       </c>
       <c r="F18" s="1">
-        <v>3.036550925925926E-3</v>
+        <v>3.0620833333333338E-3</v>
       </c>
       <c r="G18" s="1">
-        <v>3.0687731481481482E-3</v>
+        <v>3.154618055555555E-3</v>
       </c>
       <c r="H18">
-        <f t="shared" si="2"/>
-        <v>256.34300000000002</v>
+        <f t="shared" si="6"/>
+        <v>255.16</v>
       </c>
       <c r="I18">
-        <f t="shared" si="3"/>
-        <v>257.024</v>
+        <f t="shared" si="7"/>
+        <v>257.41899999999998</v>
       </c>
       <c r="J18">
-        <f t="shared" si="4"/>
-        <v>258.24200000000002</v>
+        <f t="shared" si="8"/>
+        <v>259.197</v>
       </c>
       <c r="K18">
-        <f t="shared" si="5"/>
-        <v>262.358</v>
+        <f t="shared" si="9"/>
+        <v>264.56400000000002</v>
       </c>
       <c r="L18">
-        <f t="shared" si="6"/>
-        <v>265.142</v>
+        <f t="shared" si="10"/>
+        <v>272.55899999999997</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>2.9626851851851854E-3</v>
+        <v>2.9669328703703706E-3</v>
       </c>
       <c r="D19" s="1">
-        <v>3.0148958333333334E-3</v>
+        <v>2.9748148148148147E-3</v>
       </c>
       <c r="E19" s="1">
-        <v>3.0150578703703702E-3</v>
+        <v>2.9889120370370373E-3</v>
       </c>
       <c r="F19" s="1">
-        <v>3.0855902777777782E-3</v>
+        <v>3.036550925925926E-3</v>
       </c>
       <c r="G19" s="1">
-        <v>3.1264467592592594E-3</v>
+        <v>3.0687731481481482E-3</v>
       </c>
       <c r="H19">
-        <f t="shared" si="2"/>
-        <v>255.97600000000003</v>
+        <f t="shared" si="6"/>
+        <v>256.34300000000002</v>
       </c>
       <c r="I19">
-        <f t="shared" si="3"/>
-        <v>260.48700000000002</v>
+        <f t="shared" si="7"/>
+        <v>257.024</v>
       </c>
       <c r="J19">
-        <f t="shared" si="4"/>
-        <v>260.50099999999998</v>
+        <f t="shared" si="8"/>
+        <v>258.24200000000002</v>
       </c>
       <c r="K19">
-        <f t="shared" si="5"/>
-        <v>266.59500000000003</v>
+        <f t="shared" si="9"/>
+        <v>262.358</v>
       </c>
       <c r="L19">
-        <f t="shared" si="6"/>
-        <v>270.125</v>
+        <f t="shared" si="10"/>
+        <v>265.142</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="1">
-        <v>3.0453125000000003E-3</v>
+        <v>2.9626851851851854E-3</v>
       </c>
       <c r="D20" s="1">
-        <v>3.056076388888889E-3</v>
+        <v>3.0148958333333334E-3</v>
       </c>
       <c r="E20" s="1">
-        <v>3.0578472222222218E-3</v>
+        <v>3.0150578703703702E-3</v>
       </c>
       <c r="F20" s="1">
-        <v>3.0907638888888894E-3</v>
+        <v>3.0855902777777782E-3</v>
       </c>
       <c r="G20" s="1">
-        <v>3.1762037037037037E-3</v>
+        <v>3.1264467592592594E-3</v>
       </c>
       <c r="H20">
-        <f t="shared" si="2"/>
-        <v>263.11500000000001</v>
+        <f t="shared" si="6"/>
+        <v>255.97600000000003</v>
       </c>
       <c r="I20">
-        <f t="shared" si="3"/>
-        <v>264.04500000000002</v>
+        <f t="shared" si="7"/>
+        <v>260.48700000000002</v>
       </c>
       <c r="J20">
-        <f t="shared" si="4"/>
-        <v>264.19799999999998</v>
+        <f t="shared" si="8"/>
+        <v>260.50099999999998</v>
       </c>
       <c r="K20">
-        <f t="shared" si="5"/>
-        <v>267.04200000000003</v>
+        <f t="shared" si="9"/>
+        <v>266.59500000000003</v>
       </c>
       <c r="L20">
-        <f t="shared" si="6"/>
-        <v>274.42399999999998</v>
+        <f t="shared" si="10"/>
+        <v>270.125</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="1">
-        <v>3.0764699074074075E-3</v>
+        <v>3.0453125000000003E-3</v>
       </c>
       <c r="D21" s="1">
-        <v>3.1117824074074073E-3</v>
+        <v>3.056076388888889E-3</v>
       </c>
       <c r="E21" s="1">
-        <v>3.1127662037037035E-3</v>
+        <v>3.0578472222222218E-3</v>
       </c>
       <c r="F21" s="1">
-        <v>3.1498379629629632E-3</v>
+        <v>3.0907638888888894E-3</v>
       </c>
       <c r="G21" s="1">
-        <v>3.2679513888888888E-3</v>
+        <v>3.1762037037037037E-3</v>
       </c>
       <c r="H21">
-        <f t="shared" si="2"/>
-        <v>265.80700000000002</v>
+        <f t="shared" si="6"/>
+        <v>263.11500000000001</v>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
-        <v>268.858</v>
+        <f t="shared" si="7"/>
+        <v>264.04500000000002</v>
       </c>
       <c r="J21">
-        <f t="shared" si="4"/>
-        <v>268.94299999999998</v>
+        <f t="shared" si="8"/>
+        <v>264.19799999999998</v>
       </c>
       <c r="K21">
-        <f t="shared" si="5"/>
-        <v>272.14600000000002</v>
+        <f t="shared" si="9"/>
+        <v>267.04200000000003</v>
       </c>
       <c r="L21">
-        <f t="shared" si="6"/>
-        <v>282.351</v>
+        <f t="shared" si="10"/>
+        <v>274.42399999999998</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="1">
-        <v>3.0054513888888887E-3</v>
+        <v>3.0764699074074075E-3</v>
       </c>
       <c r="D22" s="1">
-        <v>3.0269675925925924E-3</v>
+        <v>3.1117824074074073E-3</v>
       </c>
       <c r="E22" s="1">
-        <v>3.0313888888888886E-3</v>
+        <v>3.1127662037037035E-3</v>
       </c>
       <c r="F22" s="1">
-        <v>3.0745138888888888E-3</v>
+        <v>3.1498379629629632E-3</v>
       </c>
       <c r="G22" s="1">
-        <v>3.1596064814814816E-3</v>
+        <v>3.2679513888888888E-3</v>
       </c>
       <c r="H22">
-        <f t="shared" si="2"/>
-        <v>259.67099999999999</v>
+        <f t="shared" si="6"/>
+        <v>265.80700000000002</v>
       </c>
       <c r="I22">
-        <f t="shared" si="3"/>
-        <v>261.52999999999997</v>
+        <f t="shared" si="7"/>
+        <v>268.858</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
-        <v>261.91199999999998</v>
+        <f t="shared" si="8"/>
+        <v>268.94299999999998</v>
       </c>
       <c r="K22">
-        <f t="shared" si="5"/>
-        <v>265.63799999999998</v>
+        <f t="shared" si="9"/>
+        <v>272.14600000000002</v>
       </c>
       <c r="L22">
-        <f t="shared" si="6"/>
-        <v>272.99</v>
+        <f t="shared" si="10"/>
+        <v>282.351</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="1">
-        <v>2.9784953703703701E-3</v>
+        <v>3.0054513888888887E-3</v>
       </c>
       <c r="D23" s="1">
-        <v>3.0303472222222225E-3</v>
+        <v>3.0269675925925924E-3</v>
       </c>
       <c r="E23" s="1">
-        <v>3.0317245370370368E-3</v>
+        <v>3.0313888888888886E-3</v>
       </c>
       <c r="F23" s="1">
-        <v>3.0813425925925926E-3</v>
+        <v>3.0745138888888888E-3</v>
       </c>
       <c r="G23" s="1">
-        <v>3.1530439814814815E-3</v>
+        <v>3.1596064814814816E-3</v>
       </c>
       <c r="H23">
-        <f t="shared" si="2"/>
-        <v>257.34199999999998</v>
+        <f t="shared" si="6"/>
+        <v>259.67099999999999</v>
       </c>
       <c r="I23">
-        <f t="shared" si="3"/>
-        <v>261.822</v>
+        <f t="shared" si="7"/>
+        <v>261.52999999999997</v>
       </c>
       <c r="J23">
-        <f t="shared" si="4"/>
-        <v>261.94099999999997</v>
+        <f t="shared" si="8"/>
+        <v>261.91199999999998</v>
       </c>
       <c r="K23">
-        <f t="shared" si="5"/>
-        <v>266.22800000000001</v>
+        <f t="shared" si="9"/>
+        <v>265.63799999999998</v>
       </c>
       <c r="L23">
-        <f t="shared" si="6"/>
-        <v>272.423</v>
+        <f t="shared" si="10"/>
+        <v>272.99</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="1">
-        <v>3.001041666666667E-3</v>
+        <v>2.9784953703703701E-3</v>
       </c>
       <c r="D24" s="1">
-        <v>3.0223495370370365E-3</v>
+        <v>3.0303472222222225E-3</v>
       </c>
       <c r="E24" s="1">
-        <v>3.037835648148148E-3</v>
+        <v>3.0317245370370368E-3</v>
       </c>
       <c r="F24" s="1">
-        <v>3.0830902777777779E-3</v>
+        <v>3.0813425925925926E-3</v>
       </c>
       <c r="G24" s="1">
-        <v>3.1568518518518521E-3</v>
+        <v>3.1530439814814815E-3</v>
       </c>
       <c r="H24">
-        <f t="shared" si="2"/>
-        <v>259.29000000000002</v>
+        <f t="shared" si="6"/>
+        <v>257.34199999999998</v>
       </c>
       <c r="I24">
-        <f t="shared" si="3"/>
-        <v>261.13099999999997</v>
+        <f t="shared" si="7"/>
+        <v>261.822</v>
       </c>
       <c r="J24">
-        <f t="shared" si="4"/>
-        <v>262.46899999999999</v>
+        <f t="shared" si="8"/>
+        <v>261.94099999999997</v>
       </c>
       <c r="K24">
-        <f t="shared" si="5"/>
-        <v>266.37900000000002</v>
+        <f t="shared" si="9"/>
+        <v>266.22800000000001</v>
       </c>
       <c r="L24">
-        <f t="shared" si="6"/>
-        <v>272.75200000000001</v>
+        <f t="shared" si="10"/>
+        <v>272.423</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="1">
-        <v>3.079837962962963E-3</v>
+        <v>3.001041666666667E-3</v>
       </c>
       <c r="D25" s="1">
-        <v>3.0996180555555555E-3</v>
+        <v>3.0223495370370365E-3</v>
       </c>
       <c r="E25" s="1">
-        <v>3.1477893518518517E-3</v>
+        <v>3.037835648148148E-3</v>
       </c>
       <c r="F25" s="1">
-        <v>3.1896759259259261E-3</v>
+        <v>3.0830902777777779E-3</v>
       </c>
       <c r="G25" s="1">
-        <v>3.231701388888889E-3</v>
+        <v>3.1568518518518521E-3</v>
       </c>
       <c r="H25">
-        <f t="shared" si="2"/>
-        <v>266.09800000000001</v>
+        <f t="shared" si="6"/>
+        <v>259.29000000000002</v>
       </c>
       <c r="I25">
-        <f t="shared" si="3"/>
-        <v>267.80700000000002</v>
+        <f t="shared" si="7"/>
+        <v>261.13099999999997</v>
       </c>
       <c r="J25">
-        <f t="shared" si="4"/>
-        <v>271.96899999999999</v>
+        <f t="shared" si="8"/>
+        <v>262.46899999999999</v>
       </c>
       <c r="K25">
-        <f t="shared" si="5"/>
-        <v>275.58800000000002</v>
+        <f t="shared" si="9"/>
+        <v>266.37900000000002</v>
       </c>
       <c r="L25">
-        <f t="shared" si="6"/>
-        <v>279.21899999999999</v>
+        <f t="shared" si="10"/>
+        <v>272.75200000000001</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26">
+        <v>2001</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3.079837962962963E-3</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3.0996180555555555E-3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3.1477893518518517E-3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3.1896759259259261E-3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3.231701388888889E-3</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="6"/>
+        <v>266.09800000000001</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="7"/>
+        <v>267.80700000000002</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="8"/>
+        <v>271.96899999999999</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="9"/>
+        <v>275.58800000000002</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="10"/>
+        <v>279.21899999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27">
         <v>2000</v>
       </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="1">
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1">
         <v>3.0448958333333335E-3</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>3.0559722222222221E-3</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E27" s="1">
         <v>3.0654166666666664E-3</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F27" s="1">
         <v>3.1504050925925927E-3</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26">
-        <f t="shared" si="2"/>
+      <c r="G27" s="1"/>
+      <c r="H27">
+        <f t="shared" si="6"/>
         <v>263.07900000000001</v>
       </c>
-      <c r="I26">
-        <f t="shared" si="3"/>
+      <c r="I27">
+        <f t="shared" si="7"/>
         <v>264.036</v>
       </c>
-      <c r="J26">
-        <f t="shared" si="4"/>
+      <c r="J27">
+        <f t="shared" si="8"/>
         <v>264.85199999999998</v>
       </c>
-      <c r="K26">
-        <f t="shared" si="5"/>
+      <c r="K27">
+        <f t="shared" si="9"/>
         <v>272.19499999999999</v>
       </c>
     </row>
